--- a/sample/경인쇄 10절.xlsx
+++ b/sample/경인쇄 10절.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCA5170B-E9E7-49EE-9BBB-14C86CC82688}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0371E255-8AF7-416A-BB6A-A965871A0F4D}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A4일경우" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>견   적   서</t>
   </si>
@@ -116,9 +115,6 @@
     <t>표지(4도,무광코팅)</t>
   </si>
   <si>
-    <t xml:space="preserve"> * 75 %</t>
-  </si>
-  <si>
     <t>스노우250g</t>
   </si>
   <si>
@@ -126,9 +122,6 @@
   </si>
   <si>
     <t>미색모조80g</t>
-  </si>
-  <si>
-    <t>디지털마스타비</t>
   </si>
   <si>
     <t>소   계</t>
@@ -171,29 +164,35 @@
     <t>상    호</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
+  <si>
+    <t>표지디자인</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
-    <numFmt numFmtId="177" formatCode="yyyy\.\ mm\.\ dd"/>
-    <numFmt numFmtId="178" formatCode="yyyy\.\ m\.\ d"/>
-    <numFmt numFmtId="180" formatCode="[$₩-412]#,##0"/>
-    <numFmt numFmtId="183" formatCode="#,##0\ &quot; P&quot;"/>
-    <numFmt numFmtId="184" formatCode="#,##0&quot; 부&quot;"/>
-    <numFmt numFmtId="185" formatCode="&quot;* {&quot;\ #,##0"/>
-    <numFmt numFmtId="186" formatCode="&quot;+(&quot;#,##0&quot;/10 × 183)}&quot;"/>
-    <numFmt numFmtId="187" formatCode="&quot; × &quot;\ #,##0"/>
-    <numFmt numFmtId="189" formatCode="&quot;* {(8,180-&quot;#,##0&quot;)+&quot;"/>
-    <numFmt numFmtId="190" formatCode="&quot;* {(12150-&quot;#,##0&quot;)+&quot;"/>
-    <numFmt numFmtId="192" formatCode="&quot;×&quot;\ #,##0&quot;P&quot;"/>
-    <numFmt numFmtId="193" formatCode="&quot;(&quot;#,##0&quot;/10×157)}&quot;"/>
-    <numFmt numFmtId="195" formatCode="&quot;(&quot;#,##0&quot;/10 × 101)}&quot;"/>
-    <numFmt numFmtId="196" formatCode="&quot; × &quot;\ #,##0&quot; P&quot;"/>
-    <numFmt numFmtId="197" formatCode="\▽\ #,##0"/>
-    <numFmt numFmtId="198" formatCode="&quot;* 3,000 x &quot;\ #,##0\P\ "/>
-    <numFmt numFmtId="199" formatCode="\△#,##0"/>
+  <numFmts count="19">
+    <numFmt numFmtId="176" formatCode="yyyy\.\ mm\.\ dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\.\ m\.\ d"/>
+    <numFmt numFmtId="178" formatCode="[$₩-412]#,##0"/>
+    <numFmt numFmtId="179" formatCode="#,##0\ &quot; P&quot;"/>
+    <numFmt numFmtId="180" formatCode="#,##0&quot; 부&quot;"/>
+    <numFmt numFmtId="181" formatCode="&quot;* {&quot;\ #,##0"/>
+    <numFmt numFmtId="182" formatCode="&quot;+(&quot;#,##0&quot;/10 × 183)}&quot;"/>
+    <numFmt numFmtId="183" formatCode="&quot; × &quot;\ #,##0"/>
+    <numFmt numFmtId="184" formatCode="&quot;* {(8,180-&quot;#,##0&quot;)+&quot;"/>
+    <numFmt numFmtId="185" formatCode="&quot;* {(12150-&quot;#,##0&quot;)+&quot;"/>
+    <numFmt numFmtId="186" formatCode="&quot;×&quot;\ #,##0&quot;P&quot;"/>
+    <numFmt numFmtId="187" formatCode="&quot;(&quot;#,##0&quot;/10×157)}&quot;"/>
+    <numFmt numFmtId="188" formatCode="&quot;(&quot;#,##0&quot;/10 × 101)}&quot;"/>
+    <numFmt numFmtId="189" formatCode="&quot; × &quot;\ #,##0&quot; P&quot;"/>
+    <numFmt numFmtId="190" formatCode="\▽\ #,##0"/>
+    <numFmt numFmtId="191" formatCode="&quot;* 3,000 x &quot;\ #,##0\P\ "/>
+    <numFmt numFmtId="192" formatCode="\△#,##0"/>
+    <numFmt numFmtId="194" formatCode="&quot;* 1식 × &quot;\ #,##0"/>
+    <numFmt numFmtId="195" formatCode="&quot;×&quot;\ #,##0&quot;%&quot;"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -1205,7 +1204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1233,7 +1232,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1287,10 +1286,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1303,26 +1302,23 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="185" fontId="3" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="192" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="193" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="196" fontId="3" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="3" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1334,39 +1330,189 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="199" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="192" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="191" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="192" fontId="11" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="9" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1375,8 +1521,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1389,7 +1538,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1404,163 +1552,23 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="12" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="194" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="194" fontId="3" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="194" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="195" fontId="3" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="189" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="197" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="199" fontId="11" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="198" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1946,13 +1954,13 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="134"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -1963,11 +1971,11 @@
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="137"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -1993,123 +2001,123 @@
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="75">
+      <c r="B4" s="138">
         <v>46190</v>
       </c>
-      <c r="C4" s="58"/>
+      <c r="C4" s="86"/>
       <c r="D4" s="13"/>
-      <c r="E4" s="154" t="s">
-        <v>42</v>
+      <c r="E4" s="139" t="s">
+        <v>40</v>
       </c>
-      <c r="F4" s="155" t="s">
-        <v>43</v>
+      <c r="F4" s="49" t="s">
+        <v>41</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="80"/>
+      <c r="H4" s="144"/>
       <c r="I4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="81" t="s">
+      <c r="J4" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="82"/>
-      <c r="L4" s="83"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="82"/>
       <c r="M4" s="15"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="147" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="58"/>
+      <c r="B5" s="86"/>
       <c r="C5" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="17"/>
-      <c r="E5" s="76"/>
+      <c r="E5" s="140"/>
       <c r="F5" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="125" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="61"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="58"/>
       <c r="M5" s="19"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="58"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="86"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="77"/>
+      <c r="E6" s="141"/>
       <c r="F6" s="18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="61"/>
+      <c r="H6" s="127"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="58"/>
       <c r="M6" s="19"/>
     </row>
     <row r="7" spans="1:13" ht="30" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="88" t="str">
+      <c r="B7" s="151" t="str">
         <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
-        <v>이백팔십육만육천육백원정</v>
+        <v>이백육십칠만구천육백원정</v>
       </c>
-      <c r="C7" s="89"/>
+      <c r="C7" s="152"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="76"/>
+      <c r="E7" s="140"/>
       <c r="F7" s="18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
-      <c r="G7" s="63" t="s">
+      <c r="G7" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="64"/>
+      <c r="H7" s="129"/>
       <c r="I7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="63" t="s">
+      <c r="J7" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="60"/>
-      <c r="L7" s="61"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="58"/>
       <c r="M7" s="23"/>
     </row>
     <row r="8" spans="1:13" ht="30" customHeight="1">
-      <c r="A8" s="86"/>
-      <c r="B8" s="65">
+      <c r="A8" s="149"/>
+      <c r="B8" s="130">
         <f>J12</f>
-        <v>2866600</v>
+        <v>2679600</v>
       </c>
-      <c r="C8" s="58"/>
+      <c r="C8" s="86"/>
       <c r="D8" s="24"/>
-      <c r="E8" s="78"/>
+      <c r="E8" s="142"/>
       <c r="F8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="68"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="65"/>
       <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" ht="17.25">
@@ -2128,89 +2136,89 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="93" t="s">
+      <c r="C10" s="103"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="94" t="s">
+      <c r="F10" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="91"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="95" t="s">
+      <c r="G10" s="103"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="96">
+      <c r="J10" s="111">
         <v>340</v>
       </c>
-      <c r="K10" s="91"/>
-      <c r="L10" s="97"/>
+      <c r="K10" s="103"/>
+      <c r="L10" s="112"/>
       <c r="M10" s="31"/>
     </row>
     <row r="11" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A11" s="100"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="98"/>
+      <c r="A11" s="94"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="76"/>
       <c r="M11" s="31"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="103" t="str">
+      <c r="B12" s="70" t="str">
         <f>A5</f>
         <v>한국조세재정연구원</v>
       </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="107" t="s">
+      <c r="C12" s="51"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="109">
+      <c r="F12" s="121">
         <v>30</v>
       </c>
-      <c r="G12" s="55"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="110" t="s">
+      <c r="G12" s="51"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="111">
+      <c r="J12" s="123">
         <f>I33</f>
-        <v>2866600</v>
+        <v>2679600</v>
       </c>
-      <c r="K12" s="55"/>
-      <c r="L12" s="112"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="99"/>
       <c r="M12" s="32"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A13" s="102"/>
-      <c r="B13" s="104"/>
-      <c r="C13" s="105"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="104"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="113"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="120"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="124"/>
       <c r="M13" s="32"/>
     </row>
     <row r="14" spans="1:13" ht="16.5" customHeight="1">
@@ -2232,29 +2240,29 @@
       <c r="A15" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="124" t="s">
+      <c r="B15" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="125"/>
-      <c r="D15" s="124" t="s">
+      <c r="C15" s="88"/>
+      <c r="D15" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="127" t="s">
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="125"/>
-      <c r="K15" s="124" t="s">
+      <c r="J15" s="88"/>
+      <c r="K15" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="128"/>
+      <c r="L15" s="91"/>
       <c r="M15" s="19"/>
     </row>
     <row r="16" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A16" s="129" t="s">
+      <c r="A16" s="92" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="35" t="s">
@@ -2264,338 +2272,337 @@
       <c r="D16" s="37">
         <v>15370</v>
       </c>
-      <c r="E16" s="122">
+      <c r="E16" s="85">
         <f>IF(F12&gt;50,F12-50,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="58"/>
+      <c r="F16" s="86"/>
       <c r="G16" s="38">
         <v>20</v>
       </c>
-      <c r="H16" s="39" t="s">
-        <v>31</v>
+      <c r="H16" s="158">
+        <v>80</v>
       </c>
-      <c r="I16" s="114">
+      <c r="I16" s="83">
         <f>(D16+((E16/10)*183))*G16*75%</f>
         <v>230550</v>
       </c>
-      <c r="J16" s="53"/>
-      <c r="K16" s="131" t="s">
+      <c r="J16" s="84"/>
+      <c r="K16" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="76"/>
+      <c r="M16" s="19"/>
+    </row>
+    <row r="17" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A17" s="93"/>
+      <c r="B17" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="98"/>
-      <c r="M16" s="19"/>
-    </row>
-    <row r="17" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A17" s="130"/>
-      <c r="B17" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="41"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="153">
         <v>3500</v>
       </c>
-      <c r="E17" s="58"/>
-      <c r="F17" s="43">
+      <c r="E17" s="154"/>
+      <c r="F17" s="42">
         <f>IF(F12&gt;50,F12-50,0)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="41">
         <f>J10</f>
         <v>340</v>
       </c>
-      <c r="H17" s="39" t="s">
-        <v>31</v>
+      <c r="H17" s="158">
+        <v>80</v>
       </c>
-      <c r="I17" s="114">
+      <c r="I17" s="83">
         <f>((12150-D17)+((F17/10)*157))*G17*75%</f>
         <v>2205750</v>
       </c>
-      <c r="J17" s="53"/>
-      <c r="K17" s="115" t="s">
+      <c r="J17" s="84"/>
+      <c r="K17" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="76"/>
+      <c r="M17" s="19"/>
+    </row>
+    <row r="18" spans="1:13" ht="26.25" hidden="1" customHeight="1">
+      <c r="A18" s="94"/>
+      <c r="B18" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="40"/>
+      <c r="D18" s="155">
+        <v>0</v>
+      </c>
+      <c r="E18" s="156"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="156"/>
+      <c r="H18" s="157"/>
+      <c r="I18" s="83">
+        <f>D18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="84"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="76"/>
+      <c r="M18" s="19"/>
+    </row>
+    <row r="19" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A19" s="44"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="76"/>
+      <c r="M19" s="19"/>
+    </row>
+    <row r="20" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A20" s="44"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="75"/>
+      <c r="L20" s="76"/>
+      <c r="M20" s="19"/>
+    </row>
+    <row r="21" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A21" s="44"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="76"/>
+      <c r="M21" s="19"/>
+    </row>
+    <row r="22" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A22" s="44"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="83"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="19"/>
+    </row>
+    <row r="23" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A23" s="44"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="86"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="83"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="75"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="19"/>
+    </row>
+    <row r="24" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A24" s="44"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="76"/>
+      <c r="M24" s="19"/>
+    </row>
+    <row r="25" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A25" s="44"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="76"/>
+      <c r="M25" s="19"/>
+    </row>
+    <row r="26" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A26" s="44"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="96"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="83"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="76"/>
+      <c r="M26" s="19"/>
+    </row>
+    <row r="27" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A27" s="44"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="83"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="75"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="19"/>
+    </row>
+    <row r="28" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A28" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="L17" s="98"/>
-      <c r="M17" s="19"/>
-    </row>
-    <row r="18" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="40" t="s">
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="77">
+        <f>SUM(I16:J27)</f>
+        <v>2436300</v>
+      </c>
+      <c r="J28" s="55"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="45"/>
+    </row>
+    <row r="29" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A29" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="123" t="str">
-        <f>CONCATENATE(J10,"P * 500")</f>
-        <v>340P * 500</v>
+      <c r="B29" s="54"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="68">
+        <v>1</v>
       </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="114">
-        <f>J10*500</f>
-        <v>170000</v>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="78">
+        <f>ROUND(I28*D29,0)</f>
+        <v>2436300</v>
       </c>
-      <c r="J18" s="53"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="19"/>
-    </row>
-    <row r="19" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A19" s="45"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="114"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="115"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="19"/>
-    </row>
-    <row r="20" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A20" s="45"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="98"/>
-      <c r="M20" s="19"/>
-    </row>
-    <row r="21" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A21" s="45"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="115"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="19"/>
-    </row>
-    <row r="22" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A22" s="45"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="115"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="19"/>
-    </row>
-    <row r="23" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A23" s="45"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="116"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="115"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="19"/>
-    </row>
-    <row r="24" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A24" s="45"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="116"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="114"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="115"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="19"/>
-    </row>
-    <row r="25" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A25" s="45"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="114"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="115"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="19"/>
-    </row>
-    <row r="26" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A26" s="45"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="114"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="115"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="19"/>
-    </row>
-    <row r="27" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A27" s="45"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="114"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="19"/>
-    </row>
-    <row r="28" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A28" s="146" t="s">
+      <c r="J29" s="55"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="46"/>
+    </row>
+    <row r="30" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A30" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="57"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="132">
-        <f>SUM(I16:J27)</f>
-        <v>2606300</v>
-      </c>
-      <c r="J28" s="50"/>
-      <c r="K28" s="121"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="46"/>
-    </row>
-    <row r="29" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A29" s="147" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="148">
-        <v>1</v>
-      </c>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="133">
-        <f>ROUND(I28*D29,0)</f>
-        <v>2606300</v>
-      </c>
-      <c r="J29" s="50"/>
-      <c r="K29" s="119"/>
-      <c r="L29" s="61"/>
-      <c r="M29" s="47"/>
-    </row>
-    <row r="30" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A30" s="149" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="55"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="134">
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="79">
         <f>VALUE(RIGHT(I29,3))</f>
         <v>300</v>
       </c>
-      <c r="J30" s="51"/>
-      <c r="K30" s="120"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="47"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="98"/>
+      <c r="L30" s="99"/>
+      <c r="M30" s="46"/>
     </row>
     <row r="31" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A31" s="150" t="s">
+      <c r="A31" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="72"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="80">
+        <f>I29-I30</f>
+        <v>2436000</v>
+      </c>
+      <c r="J31" s="73"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="82"/>
+      <c r="M31" s="47"/>
+    </row>
+    <row r="32" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A32" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="56">
+        <f>I31*0.1</f>
+        <v>243600</v>
+      </c>
+      <c r="J32" s="55"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="48"/>
+    </row>
+    <row r="33" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A33" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="151"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="151"/>
-      <c r="F31" s="151"/>
-      <c r="G31" s="151"/>
-      <c r="H31" s="136"/>
-      <c r="I31" s="135">
-        <f>I29-I30</f>
-        <v>2606000</v>
+      <c r="B33" s="60"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="63">
+        <f>I31+I32</f>
+        <v>2679600</v>
       </c>
-      <c r="J31" s="136"/>
-      <c r="K31" s="137"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="48"/>
-    </row>
-    <row r="32" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A32" s="138" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="55"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="139">
-        <f>I31*0.1</f>
-        <v>260600</v>
-      </c>
-      <c r="J32" s="50"/>
-      <c r="K32" s="140"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="49"/>
-    </row>
-    <row r="33" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A33" s="141" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="142"/>
-      <c r="C33" s="143"/>
-      <c r="D33" s="144"/>
-      <c r="E33" s="142"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="142"/>
-      <c r="H33" s="143"/>
-      <c r="I33" s="145">
-        <f>I31+I32</f>
-        <v>2866600</v>
-      </c>
-      <c r="J33" s="143"/>
-      <c r="K33" s="66"/>
-      <c r="L33" s="68"/>
+      <c r="J33" s="61"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="65"/>
       <c r="M33" s="23"/>
     </row>
     <row r="34" spans="1:13" ht="13.5">
@@ -16879,7 +16886,93 @@
       <c r="M985" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="102">
+  <mergeCells count="101">
+    <mergeCell ref="D1:H2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:L13"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:L11"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K28:L28"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="I32:J32"/>
@@ -16895,98 +16988,11 @@
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="D31:H31"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:L11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:H13"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:L13"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="D1:H2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/sample/경인쇄 10절.xlsx
+++ b/sample/경인쇄 10절.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0371E255-8AF7-416A-BB6A-A965871A0F4D}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6C9BD7-CFC9-4356-A0DA-D9A80BD0FD1B}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="28770" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A4일경우" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>견   적   서</t>
   </si>
@@ -112,13 +112,7 @@
     <t>편집/인쇄</t>
   </si>
   <si>
-    <t>표지(4도,무광코팅)</t>
-  </si>
-  <si>
     <t>스노우250g</t>
-  </si>
-  <si>
-    <t>내지(1도, 흑백)</t>
   </si>
   <si>
     <t>미색모조80g</t>
@@ -168,6 +162,76 @@
     <t>표지디자인</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
+  <si>
+    <t>표지</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무광코팅</t>
+    </r>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>내지</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흑백</t>
+    </r>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -181,7 +245,6 @@
     <numFmt numFmtId="180" formatCode="#,##0&quot; 부&quot;"/>
     <numFmt numFmtId="181" formatCode="&quot;* {&quot;\ #,##0"/>
     <numFmt numFmtId="182" formatCode="&quot;+(&quot;#,##0&quot;/10 × 183)}&quot;"/>
-    <numFmt numFmtId="183" formatCode="&quot; × &quot;\ #,##0"/>
     <numFmt numFmtId="184" formatCode="&quot;* {(8,180-&quot;#,##0&quot;)+&quot;"/>
     <numFmt numFmtId="185" formatCode="&quot;* {(12150-&quot;#,##0&quot;)+&quot;"/>
     <numFmt numFmtId="186" formatCode="&quot;×&quot;\ #,##0&quot;P&quot;"/>
@@ -191,10 +254,11 @@
     <numFmt numFmtId="190" formatCode="\▽\ #,##0"/>
     <numFmt numFmtId="191" formatCode="&quot;* 3,000 x &quot;\ #,##0\P\ "/>
     <numFmt numFmtId="192" formatCode="\△#,##0"/>
-    <numFmt numFmtId="194" formatCode="&quot;* 1식 × &quot;\ #,##0"/>
-    <numFmt numFmtId="195" formatCode="&quot;×&quot;\ #,##0&quot;%&quot;"/>
+    <numFmt numFmtId="193" formatCode="&quot;* 1식 × &quot;\ #,##0"/>
+    <numFmt numFmtId="194" formatCode="&quot;×&quot;\ #,##0&quot;%&quot;"/>
+    <numFmt numFmtId="195" formatCode="&quot; × &quot;\ #,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -304,6 +368,17 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1204,7 +1279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1301,11 +1376,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="181" fontId="3" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1338,6 +1409,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="194" fontId="3" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1394,10 +1474,6 @@
     <xf numFmtId="191" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1418,19 +1494,20 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1442,16 +1519,7 @@
     <xf numFmtId="188" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="184" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1476,6 +1544,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="193" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="193" fontId="3" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="193" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1552,23 +1647,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="185" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="194" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="3" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="194" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1954,13 +2034,13 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="132" t="s">
+      <c r="D1" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="134"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="140"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -1971,11 +2051,11 @@
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="136"/>
-      <c r="F2" s="136"/>
-      <c r="G2" s="136"/>
-      <c r="H2" s="137"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="143"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -2001,123 +2081,123 @@
       <c r="A4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="138">
+      <c r="B4" s="144">
         <v>46190</v>
       </c>
-      <c r="C4" s="86"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="13"/>
-      <c r="E4" s="139" t="s">
-        <v>40</v>
+      <c r="E4" s="145" t="s">
+        <v>38</v>
       </c>
-      <c r="F4" s="49" t="s">
-        <v>41</v>
+      <c r="F4" s="47" t="s">
+        <v>39</v>
       </c>
-      <c r="G4" s="143" t="s">
+      <c r="G4" s="149" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="144"/>
+      <c r="H4" s="150"/>
       <c r="I4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="145" t="s">
+      <c r="J4" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="146"/>
-      <c r="L4" s="82"/>
+      <c r="K4" s="152"/>
+      <c r="L4" s="81"/>
       <c r="M4" s="15"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="153" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="86"/>
+      <c r="B5" s="95"/>
       <c r="C5" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="17"/>
-      <c r="E5" s="140"/>
+      <c r="E5" s="146"/>
       <c r="F5" s="18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
-      <c r="G5" s="125" t="s">
+      <c r="G5" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="58"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="59"/>
       <c r="M5" s="19"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
-      <c r="A6" s="150" t="s">
+      <c r="A6" s="156" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="106"/>
-      <c r="C6" s="86"/>
+      <c r="B6" s="101"/>
+      <c r="C6" s="95"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="141"/>
+      <c r="E6" s="147"/>
       <c r="F6" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
-      <c r="G6" s="125" t="s">
+      <c r="G6" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="127"/>
-      <c r="I6" s="127"/>
-      <c r="J6" s="127"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="58"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="59"/>
       <c r="M6" s="19"/>
     </row>
     <row r="7" spans="1:13" ht="30" customHeight="1">
-      <c r="A7" s="148" t="s">
+      <c r="A7" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="151" t="str">
+      <c r="B7" s="157" t="str">
         <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
         <v>이백육십칠만구천육백원정</v>
       </c>
-      <c r="C7" s="152"/>
+      <c r="C7" s="158"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="140"/>
+      <c r="E7" s="146"/>
       <c r="F7" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
-      <c r="G7" s="128" t="s">
+      <c r="G7" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="129"/>
+      <c r="H7" s="135"/>
       <c r="I7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="128" t="s">
+      <c r="J7" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="126"/>
-      <c r="L7" s="58"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="59"/>
       <c r="M7" s="23"/>
     </row>
     <row r="8" spans="1:13" ht="30" customHeight="1">
-      <c r="A8" s="149"/>
-      <c r="B8" s="130">
+      <c r="A8" s="155"/>
+      <c r="B8" s="136">
         <f>J12</f>
         <v>2679600</v>
       </c>
-      <c r="C8" s="86"/>
+      <c r="C8" s="95"/>
       <c r="D8" s="24"/>
-      <c r="E8" s="142"/>
+      <c r="E8" s="148"/>
       <c r="F8" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="131"/>
-      <c r="K8" s="131"/>
-      <c r="L8" s="65"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="137"/>
+      <c r="K8" s="137"/>
+      <c r="L8" s="66"/>
       <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" ht="17.25">
@@ -2136,89 +2216,89 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A10" s="113" t="s">
+      <c r="A10" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="107" t="s">
+      <c r="C10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="109" t="s">
+      <c r="F10" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="103"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="110" t="s">
+      <c r="G10" s="98"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="111">
+      <c r="J10" s="106">
         <v>340</v>
       </c>
-      <c r="K10" s="103"/>
-      <c r="L10" s="112"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="107"/>
       <c r="M10" s="31"/>
     </row>
     <row r="11" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="105"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="76"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="88"/>
       <c r="M11" s="31"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A12" s="114" t="s">
+      <c r="A12" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="70" t="str">
+      <c r="B12" s="71" t="str">
         <f>A5</f>
         <v>한국조세재정연구원</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="119" t="s">
+      <c r="C12" s="52"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="121">
+      <c r="F12" s="127">
         <v>30</v>
       </c>
-      <c r="G12" s="51"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="122" t="s">
+      <c r="G12" s="52"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="123">
+      <c r="J12" s="129">
         <f>I33</f>
         <v>2679600</v>
       </c>
-      <c r="K12" s="51"/>
-      <c r="L12" s="99"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="86"/>
       <c r="M12" s="32"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A13" s="115"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="116"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="120"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="117"/>
-      <c r="L13" s="124"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="123"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="130"/>
       <c r="M13" s="32"/>
     </row>
     <row r="14" spans="1:13" ht="16.5" customHeight="1">
@@ -2240,369 +2320,373 @@
       <c r="A15" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="88"/>
-      <c r="D15" s="87" t="s">
+      <c r="C15" s="115"/>
+      <c r="D15" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="88"/>
-      <c r="I15" s="90" t="s">
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="88"/>
-      <c r="K15" s="87" t="s">
+      <c r="J15" s="115"/>
+      <c r="K15" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="91"/>
+      <c r="L15" s="118"/>
       <c r="M15" s="19"/>
     </row>
     <row r="16" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="90" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="37">
+      <c r="C16" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="36">
         <v>15370</v>
       </c>
-      <c r="E16" s="85">
+      <c r="E16" s="111">
         <f>IF(F12&gt;50,F12-50,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="86"/>
-      <c r="G16" s="38">
+      <c r="F16" s="95"/>
+      <c r="G16" s="159">
         <v>20</v>
       </c>
-      <c r="H16" s="158">
+      <c r="H16" s="48">
         <v>80</v>
       </c>
-      <c r="I16" s="83">
+      <c r="I16" s="82">
         <f>(D16+((E16/10)*183))*G16*75%</f>
         <v>230550</v>
       </c>
-      <c r="J16" s="84"/>
-      <c r="K16" s="95" t="s">
-        <v>31</v>
+      <c r="J16" s="83"/>
+      <c r="K16" s="93" t="s">
+        <v>30</v>
       </c>
-      <c r="L16" s="76"/>
+      <c r="L16" s="88"/>
       <c r="M16" s="19"/>
     </row>
     <row r="17" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="39" t="s">
-        <v>32</v>
+      <c r="A17" s="91"/>
+      <c r="B17" s="37" t="s">
+        <v>46</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="153">
+      <c r="C17" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="112">
         <v>3500</v>
       </c>
-      <c r="E17" s="154"/>
-      <c r="F17" s="42">
+      <c r="E17" s="113"/>
+      <c r="F17" s="40">
         <f>IF(F12&gt;50,F12-50,0)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="39">
         <f>J10</f>
         <v>340</v>
       </c>
-      <c r="H17" s="158">
+      <c r="H17" s="48">
         <v>80</v>
       </c>
-      <c r="I17" s="83">
+      <c r="I17" s="82">
         <f>((12150-D17)+((F17/10)*157))*G17*75%</f>
         <v>2205750</v>
       </c>
-      <c r="J17" s="84"/>
-      <c r="K17" s="75" t="s">
-        <v>33</v>
+      <c r="J17" s="83"/>
+      <c r="K17" s="87" t="s">
+        <v>31</v>
       </c>
-      <c r="L17" s="76"/>
+      <c r="L17" s="88"/>
       <c r="M17" s="19"/>
     </row>
     <row r="18" spans="1:13" ht="26.25" hidden="1" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="39" t="s">
-        <v>45</v>
+      <c r="A18" s="92"/>
+      <c r="B18" s="37" t="s">
+        <v>43</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="155">
+      <c r="C18" s="38"/>
+      <c r="D18" s="108">
         <v>0</v>
       </c>
-      <c r="E18" s="156"/>
-      <c r="F18" s="156"/>
-      <c r="G18" s="156"/>
-      <c r="H18" s="157"/>
-      <c r="I18" s="83">
+      <c r="E18" s="109"/>
+      <c r="F18" s="109"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="82">
         <f>D18</f>
         <v>0</v>
       </c>
-      <c r="J18" s="84"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="76"/>
+      <c r="J18" s="83"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="88"/>
       <c r="M18" s="19"/>
     </row>
     <row r="19" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A19" s="44"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="76"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="88"/>
       <c r="M19" s="19"/>
     </row>
     <row r="20" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A20" s="44"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="76"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="94"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="88"/>
       <c r="M20" s="19"/>
     </row>
     <row r="21" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A21" s="44"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="86"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="76"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="95"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="88"/>
       <c r="M21" s="19"/>
     </row>
     <row r="22" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A22" s="44"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="76"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="94"/>
+      <c r="G22" s="95"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="83"/>
+      <c r="K22" s="87"/>
+      <c r="L22" s="88"/>
       <c r="M22" s="19"/>
     </row>
     <row r="23" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A23" s="44"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="86"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="75"/>
-      <c r="L23" s="76"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="82"/>
+      <c r="J23" s="83"/>
+      <c r="K23" s="87"/>
+      <c r="L23" s="88"/>
       <c r="M23" s="19"/>
     </row>
     <row r="24" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A24" s="44"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="76"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="83"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="88"/>
       <c r="M24" s="19"/>
     </row>
     <row r="25" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A25" s="44"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="76"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="82"/>
+      <c r="J25" s="83"/>
+      <c r="K25" s="87"/>
+      <c r="L25" s="88"/>
       <c r="M25" s="19"/>
     </row>
     <row r="26" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A26" s="44"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="76"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="95"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="83"/>
+      <c r="K26" s="87"/>
+      <c r="L26" s="88"/>
       <c r="M26" s="19"/>
     </row>
     <row r="27" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A27" s="44"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="96"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="75"/>
-      <c r="L27" s="76"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="83"/>
+      <c r="K27" s="87"/>
+      <c r="L27" s="88"/>
       <c r="M27" s="19"/>
     </row>
     <row r="28" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A28" s="66" t="s">
-        <v>34</v>
+      <c r="A28" s="67" t="s">
+        <v>32</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="77">
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="76">
         <f>SUM(I16:J27)</f>
         <v>2436300</v>
       </c>
-      <c r="J28" s="55"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="45"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="89"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="43"/>
     </row>
     <row r="29" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A29" s="67" t="s">
-        <v>35</v>
+      <c r="A29" s="68" t="s">
+        <v>33</v>
       </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="68">
+      <c r="B29" s="55"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="69">
         <v>1</v>
       </c>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="78">
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="77">
         <f>ROUND(I28*D29,0)</f>
         <v>2436300</v>
       </c>
-      <c r="J29" s="55"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="46"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="44"/>
     </row>
     <row r="30" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A30" s="69" t="s">
-        <v>36</v>
+      <c r="A30" s="70" t="s">
+        <v>34</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="79">
+      <c r="B30" s="52"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="78">
         <f>VALUE(RIGHT(I29,3))</f>
         <v>300</v>
       </c>
-      <c r="J30" s="52"/>
-      <c r="K30" s="98"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="46"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="86"/>
+      <c r="M30" s="44"/>
     </row>
     <row r="31" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A31" s="71" t="s">
-        <v>37</v>
+      <c r="A31" s="72" t="s">
+        <v>35</v>
       </c>
-      <c r="B31" s="72"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="80">
+      <c r="B31" s="73"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="79">
         <f>I29-I30</f>
         <v>2436000</v>
       </c>
-      <c r="J31" s="73"/>
-      <c r="K31" s="81"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="47"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="81"/>
+      <c r="M31" s="45"/>
     </row>
     <row r="32" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A32" s="50" t="s">
-        <v>38</v>
+      <c r="A32" s="51" t="s">
+        <v>36</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="54"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="56">
+      <c r="B32" s="52"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="57">
         <f>I31*0.1</f>
         <v>243600</v>
       </c>
-      <c r="J32" s="55"/>
-      <c r="K32" s="57"/>
-      <c r="L32" s="58"/>
-      <c r="M32" s="48"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="59"/>
+      <c r="M32" s="46"/>
     </row>
     <row r="33" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A33" s="59" t="s">
-        <v>39</v>
+      <c r="A33" s="60" t="s">
+        <v>37</v>
       </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="63">
+      <c r="B33" s="61"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="64">
         <f>I31+I32</f>
         <v>2679600</v>
       </c>
-      <c r="J33" s="61"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="65"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="65"/>
+      <c r="L33" s="66"/>
       <c r="M33" s="23"/>
     </row>
     <row r="34" spans="1:13" ht="13.5">
@@ -16909,20 +16993,18 @@
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="G8:L8"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I20:J20"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="F10:H11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:L11"/>
     <mergeCell ref="D18:H18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F24:G24"/>
@@ -16937,12 +17019,7 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="F21:G21"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="K16:L16"/>
@@ -16952,11 +17029,13 @@
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I20:J20"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
@@ -16988,6 +17067,11 @@
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="D31:H31"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="K31:L31"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
